--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-atherosklerotisches-erstereignis.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-atherosklerotisches-erstereignis.xlsx
@@ -659,6 +659,15 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/CodeSystem/mii-cs-kardio-atherosklerotisches-ereignis"/&gt;
+    &lt;code value="ae"/&gt;
+    &lt;display value="Atherosklerotisches Ereignis"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -741,13 +750,6 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/CodeSystem/mii-cs-kardio-atherosklerotisches-ereignis"/&gt;
-  &lt;code value="ae"/&gt;
-  &lt;display value="Atherosklerotisches Ereignis"/&gt;
-&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -4046,7 +4048,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -4061,13 +4063,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4100,30 +4102,30 @@
         <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4146,13 +4148,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4203,7 +4205,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4227,7 +4229,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4238,10 +4240,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4270,7 +4272,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4311,19 +4313,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4347,7 +4349,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4358,10 +4360,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4384,19 +4386,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4406,7 +4408,7 @@
         <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>82</v>
@@ -4506,13 +4508,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4563,7 +4565,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4587,7 +4589,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4630,7 +4632,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4671,19 +4673,19 @@
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4707,7 +4709,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4866,7 +4868,7 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>248</v>
@@ -5106,7 +5108,7 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>262</v>
@@ -5348,7 +5350,7 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>278</v>
@@ -5672,7 +5674,7 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>300</v>
@@ -6719,7 +6721,7 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y38" t="s" s="2">
         <v>385</v>
@@ -6841,7 +6843,7 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y39" t="s" s="2">
         <v>396</v>
@@ -7288,13 +7290,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7345,7 +7347,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7369,7 +7371,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7412,7 +7414,7 @@
         <v>140</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>142</v>
@@ -7465,7 +7467,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7489,7 +7491,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -8043,7 +8045,7 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y49" t="s" s="2">
         <v>459</v>
@@ -8248,7 +8250,7 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>468</v>
@@ -8728,13 +8730,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8785,7 +8787,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8809,7 +8811,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8852,7 +8854,7 @@
         <v>140</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>142</v>
@@ -8905,7 +8907,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8929,7 +8931,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9125,13 +9127,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9170,13 +9172,13 @@
         <v>502</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9210,13 +9212,13 @@
         <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9267,7 +9269,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9291,7 +9293,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9334,7 +9336,7 @@
         <v>140</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>142</v>
@@ -9375,19 +9377,19 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9411,7 +9413,7 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9448,19 +9450,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9570,13 +9572,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9627,7 +9629,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9651,7 +9653,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9694,7 +9696,7 @@
         <v>140</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>142</v>
@@ -9735,19 +9737,19 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9771,7 +9773,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9930,7 +9932,7 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>248</v>
@@ -10170,7 +10172,7 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>262</v>
@@ -10412,7 +10414,7 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>278</v>
@@ -11146,13 +11148,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11203,7 +11205,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11227,7 +11229,7 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11270,7 +11272,7 @@
         <v>140</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>142</v>
@@ -11323,7 +11325,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11347,7 +11349,7 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11543,13 +11545,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11588,13 +11590,13 @@
         <v>502</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>82</v>
@@ -11628,13 +11630,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11685,7 +11687,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11709,7 +11711,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11752,7 +11754,7 @@
         <v>140</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>142</v>
@@ -11793,19 +11795,19 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11829,7 +11831,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11866,19 +11868,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11988,13 +11990,13 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12045,7 +12047,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12069,7 +12071,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12112,7 +12114,7 @@
         <v>140</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>142</v>
@@ -12153,19 +12155,19 @@
         <v>82</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12189,7 +12191,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12348,7 +12350,7 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>248</v>
@@ -12588,7 +12590,7 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>262</v>
@@ -12830,7 +12832,7 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>278</v>
@@ -13562,13 +13564,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13619,7 +13621,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13643,7 +13645,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13686,7 +13688,7 @@
         <v>140</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>142</v>
@@ -13739,7 +13741,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13763,7 +13765,7 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13959,13 +13961,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14004,13 +14006,13 @@
         <v>502</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
@@ -14044,13 +14046,13 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14101,7 +14103,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14125,7 +14127,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14168,7 +14170,7 @@
         <v>140</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>142</v>
@@ -14209,19 +14211,19 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14245,7 +14247,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14282,19 +14284,19 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14404,13 +14406,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14461,7 +14463,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14485,7 +14487,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14528,7 +14530,7 @@
         <v>140</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>142</v>
@@ -14569,19 +14571,19 @@
         <v>82</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14605,7 +14607,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14764,7 +14766,7 @@
         <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>248</v>
@@ -15004,7 +15006,7 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>262</v>
@@ -15246,7 +15248,7 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>278</v>
